--- a/Assets/Die, Die!.xlsx
+++ b/Assets/Die, Die!.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Unity Projects\Dice Wars\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D033A5-6C27-4235-AFBC-1E7939F892CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01FE860-779B-42D3-BF18-1CA8EF1512BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{42B17889-99E5-4507-B727-8253FB64B408}"/>
   </bookViews>
@@ -596,21 +596,6 @@
     <t>Immune to 'Chain Lightning'.</t>
   </si>
   <si>
-    <t>Deal 1 Wound to an enemy Die. Ignores 'Fly'. No Counter.</t>
-  </si>
-  <si>
-    <t>Deal 2 Wounds to an enemy Die. Ignores 'Fly'. No Counter.</t>
-  </si>
-  <si>
-    <t>Deal 3 Wounds to an enemy Die. Ignores 'Fly'. No Counter.</t>
-  </si>
-  <si>
-    <t>This Die cannot be targeted by enemies until next turn. Next turn: Deal 1 Wound to an enemy Die. No Counter.</t>
-  </si>
-  <si>
-    <t>This Die cannot be targeted by enemies until next turn. Next turn: Deal 2 Wounds to an enemy Die. No Counter.</t>
-  </si>
-  <si>
     <t>Play a Die of you choice with 'Tunnel' from your hand. It cannot act this turn.</t>
   </si>
   <si>
@@ -723,18 +708,6 @@
   </si>
   <si>
     <t>Ember Lungs</t>
-  </si>
-  <si>
-    <t>Deal 2 Wounds to two adjacent enemy Dice. No Counter.</t>
-  </si>
-  <si>
-    <t>Deal 3 Wounds to two adjacent enemy Dice. No Counter.</t>
-  </si>
-  <si>
-    <t>Deal 3 Wounds to an enemy Die. Then repeatly jumps to another adjacent Die, dealing 1 less each time. No Counter.</t>
-  </si>
-  <si>
-    <t>Deal 4 Wounds to an enemy Die. Then repeatly jumps to another adjacent Die, dealing 1 less each time. No Counter.</t>
   </si>
   <si>
     <t>Wounds don't lock Abilities. Has always 1 Wound.</t>
@@ -1363,12 +1336,6 @@
     <t>Remove 4 Wounds of a [living] friendly Die.</t>
   </si>
   <si>
-    <t>Instantly: This Die skips a turn. Cannot be unlearned.</t>
-  </si>
-  <si>
-    <t>Instantly: Reroll with no penalty. If 'Idle' is rolled again, this Die skips a turn. Cannot be unlearned.</t>
-  </si>
-  <si>
     <t>Instantly: Reroll with no penalty and give this Die +1 Reroll.</t>
   </si>
   <si>
@@ -1411,15 +1378,6 @@
     <t>Deal 3 Wounds to an enemy Die and reduce ist Rerolls by 3.</t>
   </si>
   <si>
-    <t>Deal 1 Wound to an enemy Die and reduce ist Rerolls by 1. Ignores 'Fly'. No Counter.</t>
-  </si>
-  <si>
-    <t>Deal 2 Wounds to an enemy Die and reduce ist Rerolls by 2. Ignores 'Fly'. No Counter.</t>
-  </si>
-  <si>
-    <t>Deal 3 Wounds to an enemy Die and reduce ist Rerolls by 3. Ignores 'Fly'. No Counter.</t>
-  </si>
-  <si>
     <t>Deal 2 Wounds to a [living] enemy Die and remove 2 Wounds of this Die.</t>
   </si>
   <si>
@@ -1516,12 +1474,6 @@
     <t>Return an enemy Die with lower Quality back to its owners hand.</t>
   </si>
   <si>
-    <t>Deal 1 Wound to all enemy Dice and reduce their Rerolls by 1 until next turn. No Counter.</t>
-  </si>
-  <si>
-    <t>Deal 2 Wounds to all enemy Dice and reduce their Rerolls by 2 until next turn. No Counter.</t>
-  </si>
-  <si>
     <t>This and and adjacent Dice cannot be targeted by enemies until next turn.</t>
   </si>
   <si>
@@ -1976,6 +1928,54 @@
   </si>
   <si>
     <t>Caravan (Many)</t>
+  </si>
+  <si>
+    <t>Deal 1 Wound to an enemy Die. Ignores 'Fly'</t>
+  </si>
+  <si>
+    <t>Deal 2 Wounds to an enemy Die. Ignores 'Fly'.</t>
+  </si>
+  <si>
+    <t>Deal 3 Wounds to an enemy Die. Ignores 'Fly'.</t>
+  </si>
+  <si>
+    <t>Deal 1 Wound to an enemy Die and reduce ist Rerolls by 1. Ignores 'Fly'.</t>
+  </si>
+  <si>
+    <t>Deal 2 Wounds to an enemy Die and reduce ist Rerolls by 2. Ignores 'Fly'.</t>
+  </si>
+  <si>
+    <t>Deal 3 Wounds to an enemy Die and reduce ist Rerolls by 3. Ignores 'Fly'.</t>
+  </si>
+  <si>
+    <t>Deal 1 Wound to all enemy Dice and reduce their Rerolls by 1 until next turn.</t>
+  </si>
+  <si>
+    <t>Deal 2 Wounds to all enemy Dice and reduce their Rerolls by 2 until next turn.</t>
+  </si>
+  <si>
+    <t>Deal 3 Wounds to two adjacent enemy Dice.</t>
+  </si>
+  <si>
+    <t>Deal 4 Wounds to an enemy Die. Then repeatly jumps to another adjacent Die, dealing 1 less each time.</t>
+  </si>
+  <si>
+    <t>Deal 3 Wounds to an enemy Die. Then repeatly jumps to another adjacent Die, dealing 1 less each time.</t>
+  </si>
+  <si>
+    <t>This Die cannot be targeted by enemies until next turn. Next turn: Deal 1 Wound to an enemy Die.</t>
+  </si>
+  <si>
+    <t>This Die cannot be targeted by enemies until next turn. Next turn: Deal 2 Wounds to an enemy Die.</t>
+  </si>
+  <si>
+    <t>Deal 2 Wounds to two adjacent enemy Dice.</t>
+  </si>
+  <si>
+    <t>Instantly: This Die skips a turn. Passive: Costs 1 less.</t>
+  </si>
+  <si>
+    <t>Instantly: Reroll with no penalty. If 'Idle' is rolled again, this Die skips a turn. Passive: Costs 1 less.</t>
   </si>
 </sst>
 </file>
@@ -2454,7 +2454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2765,9 +2765,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2779,6 +2776,24 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3115,7 +3130,9 @@
     <col min="2" max="2" width="18.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="5.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" style="2" customWidth="1"/>
-    <col min="5" max="8" width="38.7109375" style="1" customWidth="1"/>
+    <col min="5" max="6" width="38.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="49.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="41.5703125" style="1" customWidth="1"/>
     <col min="11" max="11" width="42.140625" style="1" customWidth="1"/>
@@ -3143,10 +3160,10 @@
         <v>176</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -3157,10 +3174,10 @@
     </row>
     <row r="4" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D4" s="3" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>175</v>
@@ -3186,16 +3203,16 @@
     </row>
     <row r="5" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="3" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>171</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>180</v>
@@ -3204,7 +3221,7 @@
         <v>179</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -3215,10 +3232,10 @@
     </row>
     <row r="6" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="3" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -3234,10 +3251,10 @@
     </row>
     <row r="7" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="3" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -3253,16 +3270,16 @@
     </row>
     <row r="8" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" s="3" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>55</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>47</v>
@@ -3282,10 +3299,10 @@
     </row>
     <row r="9" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="3" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>59</v>
@@ -3310,10 +3327,10 @@
     </row>
     <row r="10" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="3" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>60</v>
@@ -3328,7 +3345,7 @@
         <v>43</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -3339,10 +3356,10 @@
     </row>
     <row r="11" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="3" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>56</v>
@@ -3379,7 +3396,7 @@
         <v>46</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>51</v>
@@ -3426,7 +3443,7 @@
         <v>49</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>54</v>
@@ -3473,7 +3490,7 @@
     </row>
     <row r="17" spans="4:17" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F17" s="1" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>105</v>
@@ -3482,7 +3499,7 @@
         <v>104</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>101</v>
@@ -3493,16 +3510,16 @@
         <v>139</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="K18" s="1"/>
     </row>
@@ -3554,7 +3571,7 @@
         <v>59</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>68</v>
@@ -3578,7 +3595,7 @@
         <v>49</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>43</v>
@@ -3633,7 +3650,7 @@
     <row r="29" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="3"/>
       <c r="F29" s="1" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>105</v>
@@ -3647,16 +3664,16 @@
         <v>139</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
     </row>
     <row r="34" spans="6:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3668,7 +3685,7 @@
         <v>55</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>47</v>
@@ -3711,7 +3728,7 @@
         <v>43</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="41" spans="6:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3742,7 +3759,7 @@
         <v>46</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>51</v>
@@ -3773,7 +3790,7 @@
         <v>49</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>54</v>
@@ -3798,9 +3815,9 @@
       </c>
       <c r="J65" s="53"/>
       <c r="K65" s="53"/>
-      <c r="N65" s="104"/>
-      <c r="O65" s="104"/>
-      <c r="P65" s="104"/>
+      <c r="N65" s="108"/>
+      <c r="O65" s="108"/>
+      <c r="P65" s="108"/>
     </row>
     <row r="66" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="1"/>
@@ -3813,139 +3830,139 @@
     </row>
     <row r="67" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" s="109" t="s">
         <v>73</v>
       </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="J67" s="3"/>
+      <c r="G67" s="109"/>
+      <c r="H67" s="109" t="s">
+        <v>409</v>
+      </c>
+      <c r="I67" s="109"/>
+      <c r="J67" s="109"/>
       <c r="K67" s="3"/>
     </row>
     <row r="68" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" s="109" t="s">
         <v>74</v>
       </c>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="J68" s="3"/>
+      <c r="G68" s="109"/>
+      <c r="H68" s="109" t="s">
+        <v>410</v>
+      </c>
+      <c r="I68" s="109"/>
+      <c r="J68" s="109"/>
       <c r="K68" s="3"/>
     </row>
     <row r="69" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" s="109" t="s">
         <v>75</v>
       </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="J69" s="3"/>
+      <c r="G69" s="109"/>
+      <c r="H69" s="109" t="s">
+        <v>411</v>
+      </c>
+      <c r="I69" s="109"/>
+      <c r="J69" s="109"/>
       <c r="K69" s="3"/>
     </row>
     <row r="70" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="J70" s="3"/>
+      <c r="F70" s="109" t="s">
+        <v>596</v>
+      </c>
+      <c r="G70" s="109"/>
+      <c r="H70" s="109" t="s">
+        <v>599</v>
+      </c>
+      <c r="I70" s="109"/>
+      <c r="J70" s="109"/>
       <c r="K70" s="3"/>
     </row>
     <row r="71" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="J71" s="3"/>
+      <c r="F71" s="109" t="s">
+        <v>597</v>
+      </c>
+      <c r="G71" s="109"/>
+      <c r="H71" s="109" t="s">
+        <v>600</v>
+      </c>
+      <c r="I71" s="109"/>
+      <c r="J71" s="109"/>
       <c r="K71" s="3"/>
     </row>
     <row r="72" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="1"/>
       <c r="D72" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="J72" s="3"/>
+      <c r="F72" s="109" t="s">
+        <v>598</v>
+      </c>
+      <c r="G72" s="109"/>
+      <c r="H72" s="109" t="s">
+        <v>601</v>
+      </c>
+      <c r="I72" s="109"/>
+      <c r="J72" s="109"/>
       <c r="K72" s="3"/>
     </row>
     <row r="73" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="1"/>
       <c r="D73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
+      <c r="F73" s="109"/>
+      <c r="G73" s="109"/>
+      <c r="H73" s="109"/>
+      <c r="I73" s="109"/>
+      <c r="J73" s="109"/>
       <c r="K73" s="3"/>
     </row>
     <row r="74" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D74" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="J74" s="3"/>
+        <v>232</v>
+      </c>
+      <c r="F74" s="109" t="s">
+        <v>439</v>
+      </c>
+      <c r="G74" s="109"/>
+      <c r="H74" s="109" t="s">
+        <v>438</v>
+      </c>
+      <c r="I74" s="109"/>
+      <c r="J74" s="109"/>
       <c r="K74" s="3"/>
       <c r="P74" s="4" t="s">
         <v>10</v>
@@ -3956,20 +3973,20 @@
     </row>
     <row r="75" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D75" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="J75" s="3"/>
+      <c r="F75" s="109" t="s">
+        <v>602</v>
+      </c>
+      <c r="G75" s="109"/>
+      <c r="H75" s="109" t="s">
+        <v>603</v>
+      </c>
+      <c r="I75" s="109"/>
+      <c r="J75" s="109"/>
       <c r="K75" s="3"/>
       <c r="P75" s="4" t="s">
         <v>40</v>
@@ -3980,20 +3997,20 @@
     </row>
     <row r="76" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D76" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="J76" s="3"/>
+        <v>432</v>
+      </c>
+      <c r="F76" s="109" t="s">
+        <v>609</v>
+      </c>
+      <c r="G76" s="109"/>
+      <c r="H76" s="109" t="s">
+        <v>604</v>
+      </c>
+      <c r="I76" s="109"/>
+      <c r="J76" s="109"/>
       <c r="K76" s="3"/>
       <c r="P76" s="4" t="s">
         <v>13</v>
@@ -4004,20 +4021,20 @@
     </row>
     <row r="77" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D77" s="45" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J77" s="3"/>
+      <c r="F77" s="109" t="s">
+        <v>606</v>
+      </c>
+      <c r="G77" s="109"/>
+      <c r="H77" s="109" t="s">
+        <v>605</v>
+      </c>
+      <c r="I77" s="109"/>
+      <c r="J77" s="109"/>
       <c r="K77" s="3"/>
       <c r="P77" s="4" t="s">
         <v>11</v>
@@ -4028,20 +4045,20 @@
     </row>
     <row r="78" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="51" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="F78" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="J78" s="3"/>
+      <c r="F78" s="109" t="s">
+        <v>392</v>
+      </c>
+      <c r="G78" s="109"/>
+      <c r="H78" s="109" t="s">
+        <v>412</v>
+      </c>
+      <c r="I78" s="109"/>
+      <c r="J78" s="109"/>
       <c r="K78" s="3"/>
       <c r="P78" s="4" t="s">
         <v>4</v>
@@ -4053,31 +4070,31 @@
     <row r="79" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="8"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
+      <c r="F79" s="109"/>
+      <c r="G79" s="109"/>
+      <c r="H79" s="109"/>
+      <c r="I79" s="109"/>
+      <c r="J79" s="109"/>
       <c r="K79" s="3"/>
       <c r="P79" s="4"/>
       <c r="Q79" s="5"/>
     </row>
     <row r="80" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="49" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="J80" s="3"/>
+      <c r="F80" s="109" t="s">
+        <v>322</v>
+      </c>
+      <c r="G80" s="109"/>
+      <c r="H80" s="109" t="s">
+        <v>317</v>
+      </c>
+      <c r="I80" s="109"/>
+      <c r="J80" s="109"/>
       <c r="K80" s="3"/>
       <c r="P80" s="4" t="s">
         <v>2</v>
@@ -4088,20 +4105,20 @@
     </row>
     <row r="81" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="48" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="109" t="s">
         <v>170</v>
       </c>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="J81" s="3"/>
+      <c r="G81" s="109"/>
+      <c r="H81" s="109" t="s">
+        <v>444</v>
+      </c>
+      <c r="I81" s="109"/>
+      <c r="J81" s="109"/>
       <c r="K81" s="3"/>
       <c r="P81" s="1" t="s">
         <v>14</v>
@@ -4112,20 +4129,20 @@
     </row>
     <row r="82" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D82" s="49" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J82" s="3"/>
+      <c r="F82" s="109" t="s">
+        <v>607</v>
+      </c>
+      <c r="G82" s="109"/>
+      <c r="H82" s="109" t="s">
+        <v>608</v>
+      </c>
+      <c r="I82" s="109"/>
+      <c r="J82" s="109"/>
       <c r="K82" s="3"/>
       <c r="P82" s="4" t="s">
         <v>12</v>
@@ -4141,15 +4158,15 @@
       <c r="E83" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="J83" s="3"/>
+      <c r="F83" s="109" t="s">
+        <v>430</v>
+      </c>
+      <c r="G83" s="109"/>
+      <c r="H83" s="109" t="s">
+        <v>431</v>
+      </c>
+      <c r="I83" s="109"/>
+      <c r="J83" s="109"/>
       <c r="K83" s="3"/>
       <c r="P83" s="1"/>
       <c r="Q83" s="5"/>
@@ -4161,15 +4178,15 @@
       <c r="E84" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="J84" s="3"/>
+      <c r="F84" s="109" t="s">
+        <v>442</v>
+      </c>
+      <c r="G84" s="109"/>
+      <c r="H84" s="109" t="s">
+        <v>443</v>
+      </c>
+      <c r="I84" s="109"/>
+      <c r="J84" s="109"/>
       <c r="K84" s="3"/>
       <c r="P84" s="4"/>
       <c r="Q84" s="5">
@@ -4182,11 +4199,11 @@
     <row r="85" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="8"/>
       <c r="E85" s="4"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
+      <c r="F85" s="109"/>
+      <c r="G85" s="109"/>
+      <c r="H85" s="109"/>
+      <c r="I85" s="109"/>
+      <c r="J85" s="109"/>
       <c r="K85" s="3"/>
       <c r="P85" s="4"/>
       <c r="Q85" s="5"/>
@@ -4198,15 +4215,15 @@
       <c r="E86" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F86" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="J86" s="3"/>
+      <c r="F86" s="109" t="s">
+        <v>394</v>
+      </c>
+      <c r="G86" s="109"/>
+      <c r="H86" s="109" t="s">
+        <v>397</v>
+      </c>
+      <c r="I86" s="109"/>
+      <c r="J86" s="109"/>
       <c r="K86" s="3"/>
       <c r="P86" s="4" t="s">
         <v>41</v>
@@ -4222,15 +4239,15 @@
       <c r="E87" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F87" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="J87" s="3"/>
+      <c r="F87" s="109" t="s">
+        <v>393</v>
+      </c>
+      <c r="G87" s="109"/>
+      <c r="H87" s="109" t="s">
+        <v>395</v>
+      </c>
+      <c r="I87" s="109"/>
+      <c r="J87" s="109"/>
       <c r="K87" s="3"/>
       <c r="P87" s="4"/>
       <c r="Q87" s="5"/>
@@ -4242,15 +4259,15 @@
       <c r="E88" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="J88" s="3"/>
+      <c r="F88" s="109" t="s">
+        <v>434</v>
+      </c>
+      <c r="G88" s="109"/>
+      <c r="H88" s="109" t="s">
+        <v>435</v>
+      </c>
+      <c r="I88" s="109"/>
+      <c r="J88" s="109"/>
       <c r="K88" s="3"/>
       <c r="P88" s="4" t="s">
         <v>0</v>
@@ -4261,20 +4278,20 @@
     </row>
     <row r="89" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="46" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="J89" s="3"/>
+        <v>321</v>
+      </c>
+      <c r="F89" s="109" t="s">
+        <v>437</v>
+      </c>
+      <c r="G89" s="109"/>
+      <c r="H89" s="109" t="s">
+        <v>436</v>
+      </c>
+      <c r="I89" s="109"/>
+      <c r="J89" s="109"/>
       <c r="K89" s="3"/>
       <c r="P89" s="4" t="s">
         <v>8</v>
@@ -4290,15 +4307,15 @@
       <c r="E90" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3" t="s">
+      <c r="G90" s="109"/>
+      <c r="H90" s="109" t="s">
         <v>182</v>
       </c>
-      <c r="J90" s="3"/>
+      <c r="I90" s="109"/>
+      <c r="J90" s="109"/>
       <c r="K90" s="3"/>
       <c r="P90" s="4"/>
       <c r="Q90" s="5"/>
@@ -4306,11 +4323,11 @@
     <row r="91" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="8"/>
       <c r="E91" s="4"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
+      <c r="F91" s="109"/>
+      <c r="G91" s="109"/>
+      <c r="H91" s="109"/>
+      <c r="I91" s="109"/>
+      <c r="J91" s="109"/>
       <c r="K91" s="3"/>
     </row>
     <row r="92" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4320,15 +4337,15 @@
       <c r="E92" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F92" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="J92" s="3"/>
+      <c r="F92" s="109" t="s">
+        <v>405</v>
+      </c>
+      <c r="G92" s="109"/>
+      <c r="H92" s="109" t="s">
+        <v>406</v>
+      </c>
+      <c r="I92" s="109"/>
+      <c r="J92" s="109"/>
       <c r="K92" s="3"/>
       <c r="P92" s="1" t="s">
         <v>30</v>
@@ -4341,15 +4358,15 @@
       <c r="E93" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="J93" s="3"/>
+      <c r="F93" s="109" t="s">
+        <v>407</v>
+      </c>
+      <c r="G93" s="109"/>
+      <c r="H93" s="109" t="s">
+        <v>399</v>
+      </c>
+      <c r="I93" s="109"/>
+      <c r="J93" s="109"/>
       <c r="K93" s="3"/>
       <c r="P93" s="1" t="s">
         <v>5</v>
@@ -4365,15 +4382,15 @@
       <c r="E94" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3" t="s">
+      <c r="F94" s="109" t="s">
+        <v>408</v>
+      </c>
+      <c r="G94" s="109"/>
+      <c r="H94" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="J94" s="3"/>
+      <c r="I94" s="109"/>
+      <c r="J94" s="109"/>
       <c r="K94" s="3"/>
       <c r="P94" s="1" t="s">
         <v>9</v>
@@ -4389,15 +4406,15 @@
       <c r="E95" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F95" s="3" t="s">
+      <c r="F95" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3" t="s">
+      <c r="G95" s="109"/>
+      <c r="H95" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="J95" s="3"/>
+      <c r="I95" s="109"/>
+      <c r="J95" s="109"/>
       <c r="K95" s="3"/>
       <c r="P95" s="1" t="s">
         <v>7</v>
@@ -4411,17 +4428,17 @@
         <v>31</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="J96" s="3"/>
+        <v>323</v>
+      </c>
+      <c r="F96" s="109" t="s">
+        <v>318</v>
+      </c>
+      <c r="G96" s="109"/>
+      <c r="H96" s="109" t="s">
+        <v>319</v>
+      </c>
+      <c r="I96" s="109"/>
+      <c r="J96" s="109"/>
       <c r="K96" s="3"/>
       <c r="P96" s="1" t="s">
         <v>15</v>
@@ -4433,11 +4450,11 @@
     <row r="97" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="8"/>
       <c r="E97" s="4"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
+      <c r="F97" s="109"/>
+      <c r="G97" s="109"/>
+      <c r="H97" s="109"/>
+      <c r="I97" s="109"/>
+      <c r="J97" s="109"/>
       <c r="K97" s="3"/>
       <c r="P97" s="4"/>
       <c r="Q97" s="5"/>
@@ -4449,15 +4466,15 @@
       <c r="E98" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F98" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3" t="s">
+      <c r="F98" s="109" t="s">
+        <v>320</v>
+      </c>
+      <c r="G98" s="109"/>
+      <c r="H98" s="109" t="s">
         <v>86</v>
       </c>
-      <c r="J98" s="3"/>
+      <c r="I98" s="109"/>
+      <c r="J98" s="109"/>
       <c r="K98" s="3"/>
       <c r="P98" s="4" t="s">
         <v>1</v>
@@ -4476,15 +4493,15 @@
       <c r="E99" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F99" s="3" t="s">
+      <c r="F99" s="109" t="s">
         <v>85</v>
       </c>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="J99" s="3"/>
+      <c r="G99" s="109"/>
+      <c r="H99" s="109" t="s">
+        <v>185</v>
+      </c>
+      <c r="I99" s="109"/>
+      <c r="J99" s="109"/>
       <c r="K99" s="3"/>
       <c r="P99" s="4" t="s">
         <v>18</v>
@@ -4496,22 +4513,22 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:18" x14ac:dyDescent="0.25">
       <c r="D100" s="47" t="s">
         <v>31</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="J100" s="3"/>
+        <v>221</v>
+      </c>
+      <c r="F100" s="109" t="s">
+        <v>379</v>
+      </c>
+      <c r="G100" s="109"/>
+      <c r="H100" s="109" t="s">
+        <v>380</v>
+      </c>
+      <c r="I100" s="109"/>
+      <c r="J100" s="109"/>
       <c r="K100" s="3"/>
       <c r="P100" s="4" t="s">
         <v>16</v>
@@ -4530,15 +4547,15 @@
       <c r="E101" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="J101" s="3"/>
+      <c r="F101" s="109" t="s">
+        <v>440</v>
+      </c>
+      <c r="G101" s="109"/>
+      <c r="H101" s="109" t="s">
+        <v>441</v>
+      </c>
+      <c r="I101" s="109"/>
+      <c r="J101" s="109"/>
       <c r="K101" s="3"/>
       <c r="P101" s="4"/>
       <c r="Q101" s="5">
@@ -4555,15 +4572,15 @@
       <c r="E102" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F102" s="3" t="s">
+      <c r="F102" s="109" t="s">
         <v>81</v>
       </c>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="J102" s="3"/>
+      <c r="G102" s="109"/>
+      <c r="H102" s="109" t="s">
+        <v>398</v>
+      </c>
+      <c r="I102" s="109"/>
+      <c r="J102" s="109"/>
       <c r="K102" s="3"/>
       <c r="P102" s="4" t="s">
         <v>6</v>
@@ -4575,11 +4592,11 @@
     <row r="103" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D103" s="11"/>
       <c r="E103" s="7"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3"/>
+      <c r="F103" s="109"/>
+      <c r="G103" s="109"/>
+      <c r="H103" s="109"/>
+      <c r="I103" s="109"/>
+      <c r="J103" s="109"/>
       <c r="K103" s="3"/>
       <c r="P103" s="4"/>
       <c r="Q103" s="5"/>
@@ -4591,15 +4608,15 @@
       <c r="E104" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F104" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="J104" s="3"/>
+      <c r="F104" s="109" t="s">
+        <v>396</v>
+      </c>
+      <c r="G104" s="109"/>
+      <c r="H104" s="109" t="s">
+        <v>400</v>
+      </c>
+      <c r="I104" s="109"/>
+      <c r="J104" s="109"/>
       <c r="K104" s="3"/>
       <c r="P104" s="4" t="s">
         <v>17</v>
@@ -4619,15 +4636,15 @@
       <c r="E105" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F105" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="J105" s="3"/>
+      <c r="F105" s="109" t="s">
+        <v>401</v>
+      </c>
+      <c r="G105" s="109"/>
+      <c r="H105" s="109" t="s">
+        <v>402</v>
+      </c>
+      <c r="I105" s="109"/>
+      <c r="J105" s="109"/>
       <c r="K105" s="3"/>
       <c r="P105" s="4"/>
       <c r="Q105" s="5">
@@ -4645,15 +4662,15 @@
       <c r="E106" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F106" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
-      <c r="I106" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="J106" s="3"/>
+      <c r="F106" s="109" t="s">
+        <v>404</v>
+      </c>
+      <c r="G106" s="109"/>
+      <c r="H106" s="109" t="s">
+        <v>403</v>
+      </c>
+      <c r="I106" s="109"/>
+      <c r="J106" s="109"/>
       <c r="K106" s="3"/>
       <c r="P106" s="4" t="s">
         <v>29</v>
@@ -4667,11 +4684,11 @@
     </row>
     <row r="107" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D107" s="8"/>
-      <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
-      <c r="I107" s="3"/>
-      <c r="J107" s="3"/>
+      <c r="F107" s="109"/>
+      <c r="G107" s="109"/>
+      <c r="H107" s="109"/>
+      <c r="I107" s="109"/>
+      <c r="J107" s="109"/>
       <c r="K107" s="3"/>
       <c r="P107" s="4"/>
       <c r="Q107" s="5">
@@ -4683,20 +4700,20 @@
     </row>
     <row r="108" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D108" s="50" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F108" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
-      <c r="I108" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="J108" s="3"/>
+      <c r="F108" s="109" t="s">
+        <v>610</v>
+      </c>
+      <c r="G108" s="109"/>
+      <c r="H108" s="109" t="s">
+        <v>611</v>
+      </c>
+      <c r="I108" s="109"/>
+      <c r="J108" s="109"/>
       <c r="K108" s="3"/>
       <c r="P108" s="4" t="s">
         <v>3</v>
@@ -4710,11 +4727,11 @@
     </row>
     <row r="109" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D109" s="86"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3"/>
+      <c r="F109" s="109"/>
+      <c r="G109" s="109"/>
+      <c r="H109" s="109"/>
+      <c r="I109" s="109"/>
+      <c r="J109" s="109"/>
       <c r="K109" s="3"/>
       <c r="Q109" s="5">
         <v>0.5</v>
@@ -4728,11 +4745,11 @@
       <c r="E110" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
+      <c r="F110" s="109"/>
+      <c r="G110" s="109"/>
+      <c r="H110" s="109"/>
+      <c r="I110" s="109"/>
+      <c r="J110" s="109"/>
       <c r="K110" s="3"/>
       <c r="P110" s="4" t="s">
         <v>35</v>
@@ -4747,15 +4764,15 @@
     <row r="111" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D111" s="11"/>
       <c r="E111" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
-      <c r="J111" s="3"/>
+        <v>187</v>
+      </c>
+      <c r="F111" s="109" t="s">
+        <v>231</v>
+      </c>
+      <c r="G111" s="109"/>
+      <c r="H111" s="109"/>
+      <c r="I111" s="109"/>
+      <c r="J111" s="109"/>
       <c r="K111" s="3"/>
       <c r="P111" s="4" t="s">
         <v>36</v>
@@ -4772,13 +4789,13 @@
       <c r="E112" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F112" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3"/>
-      <c r="J112" s="3"/>
+      <c r="G112" s="109"/>
+      <c r="H112" s="109"/>
+      <c r="I112" s="109"/>
+      <c r="J112" s="109"/>
       <c r="K112" s="3"/>
       <c r="P112" s="4" t="s">
         <v>37</v>
@@ -4794,15 +4811,15 @@
     <row r="113" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D113" s="11"/>
       <c r="E113" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3"/>
-      <c r="J113" s="3"/>
+        <v>338</v>
+      </c>
+      <c r="F113" s="109" t="s">
+        <v>339</v>
+      </c>
+      <c r="G113" s="109"/>
+      <c r="H113" s="109"/>
+      <c r="I113" s="109"/>
+      <c r="J113" s="109"/>
       <c r="K113" s="3"/>
       <c r="Q113" s="5">
         <f>Q88</f>
@@ -4815,15 +4832,15 @@
     <row r="114" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D114" s="11"/>
       <c r="E114" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="F114" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F114" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3"/>
-      <c r="J114" s="3"/>
+      <c r="G114" s="109"/>
+      <c r="H114" s="109"/>
+      <c r="I114" s="109"/>
+      <c r="J114" s="109"/>
       <c r="K114" s="3"/>
       <c r="P114" s="4" t="s">
         <v>38</v>
@@ -4836,15 +4853,15 @@
     <row r="115" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D115" s="11"/>
       <c r="E115" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F115" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="F115" s="109" t="s">
         <v>80</v>
       </c>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
-      <c r="J115" s="3"/>
+      <c r="G115" s="109"/>
+      <c r="H115" s="109"/>
+      <c r="I115" s="109"/>
+      <c r="J115" s="109"/>
       <c r="K115" s="3"/>
       <c r="P115" s="4" t="s">
         <v>39</v>
@@ -4859,15 +4876,15 @@
     <row r="116" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D116" s="11"/>
       <c r="E116" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="F116" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="F116" s="109" t="s">
         <v>184</v>
       </c>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="3"/>
+      <c r="G116" s="109"/>
+      <c r="H116" s="109"/>
+      <c r="I116" s="109"/>
+      <c r="J116" s="109"/>
       <c r="K116" s="3"/>
       <c r="P116" s="4"/>
       <c r="Q116" s="5"/>
@@ -4877,13 +4894,13 @@
       <c r="E117" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F117" s="3" t="s">
+      <c r="F117" s="109" t="s">
         <v>87</v>
       </c>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
-      <c r="J117" s="3"/>
+      <c r="G117" s="109"/>
+      <c r="H117" s="109"/>
+      <c r="I117" s="109"/>
+      <c r="J117" s="109"/>
       <c r="K117" s="3"/>
       <c r="P117" s="4"/>
       <c r="Q117" s="5"/>
@@ -4893,13 +4910,13 @@
       <c r="E118" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F118" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="3"/>
+      <c r="F118" s="109" t="s">
+        <v>223</v>
+      </c>
+      <c r="G118" s="109"/>
+      <c r="H118" s="109"/>
+      <c r="I118" s="109"/>
+      <c r="J118" s="109"/>
       <c r="K118" s="3"/>
       <c r="P118" s="4"/>
       <c r="Q118" s="5"/>
@@ -4907,15 +4924,15 @@
     <row r="119" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D119" s="11"/>
       <c r="E119" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="3"/>
+        <v>384</v>
+      </c>
+      <c r="F119" s="109" t="s">
+        <v>391</v>
+      </c>
+      <c r="G119" s="109"/>
+      <c r="H119" s="109"/>
+      <c r="I119" s="109"/>
+      <c r="J119" s="109"/>
       <c r="K119" s="3"/>
       <c r="P119" s="4"/>
       <c r="Q119" s="5"/>
@@ -4925,40 +4942,43 @@
       <c r="E120" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F120" s="3" t="s">
+      <c r="F120" s="109" t="s">
         <v>88</v>
       </c>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="12"/>
+      <c r="G120" s="109"/>
+      <c r="H120" s="109"/>
+      <c r="I120" s="109"/>
+      <c r="J120" s="109"/>
       <c r="P120" s="4"/>
       <c r="Q120" s="5"/>
     </row>
     <row r="121" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D121" s="11"/>
       <c r="E121" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="G121" s="3"/>
-      <c r="H121" s="3"/>
-      <c r="I121" s="12"/>
+        <v>305</v>
+      </c>
+      <c r="F121" s="109" t="s">
+        <v>307</v>
+      </c>
+      <c r="G121" s="109"/>
+      <c r="H121" s="109"/>
+      <c r="I121" s="109"/>
+      <c r="J121" s="109"/>
       <c r="P121" s="4"/>
       <c r="Q121" s="5"/>
     </row>
     <row r="122" spans="4:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D122" s="11"/>
       <c r="E122" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="G122" s="3"/>
-      <c r="H122" s="3"/>
-      <c r="I122" s="12"/>
+        <v>224</v>
+      </c>
+      <c r="F122" s="109" t="s">
+        <v>248</v>
+      </c>
+      <c r="G122" s="109"/>
+      <c r="H122" s="109"/>
+      <c r="I122" s="109"/>
+      <c r="J122" s="109"/>
       <c r="P122" s="4"/>
       <c r="Q122" s="5"/>
     </row>
@@ -5022,13 +5042,13 @@
     <row r="129" spans="4:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D129" s="11"/>
       <c r="E129" s="15" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F129" s="16" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G129" s="14" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
@@ -5049,13 +5069,13 @@
         <v>178</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="H131" s="3"/>
       <c r="I131" s="12"/>
@@ -5067,13 +5087,13 @@
         <v>177</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="H132" s="3"/>
       <c r="I132" s="12"/>
@@ -5085,13 +5105,13 @@
         <v>176</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="H133" s="3"/>
       <c r="I133" s="12"/>
@@ -5103,13 +5123,13 @@
         <v>175</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="H134" s="3"/>
       <c r="I134" s="12"/>
@@ -5121,13 +5141,13 @@
         <v>174</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="H135" s="3"/>
       <c r="I135" s="12"/>
@@ -5139,13 +5159,13 @@
         <v>173</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H136" s="3"/>
       <c r="I136" s="12"/>
@@ -5157,13 +5177,13 @@
         <v>172</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="12"/>
@@ -5172,16 +5192,16 @@
     </row>
     <row r="138" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D138" s="3" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I138" s="12"/>
       <c r="P138" s="4"/>
@@ -5192,13 +5212,13 @@
         <v>171</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="I139" s="12"/>
       <c r="P139" s="4"/>
@@ -5209,13 +5229,13 @@
         <v>50</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I140" s="12"/>
       <c r="P140" s="4"/>
@@ -5226,13 +5246,13 @@
         <v>181</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I141" s="12"/>
       <c r="P141" s="4"/>
@@ -5243,29 +5263,29 @@
         <v>179</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="P142" s="4"/>
       <c r="Q142" s="5"/>
     </row>
     <row r="143" spans="4:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D143" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="P143" s="4"/>
       <c r="Q143" s="5"/>
@@ -5275,13 +5295,13 @@
         <v>180</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="P144" s="4"/>
       <c r="Q144" s="5"/>
@@ -5298,13 +5318,13 @@
     <row r="146" spans="3:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D146" s="11"/>
       <c r="E146" s="15" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F146" s="16" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G146" s="14" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
@@ -5314,13 +5334,13 @@
     <row r="147" spans="3:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D147" s="11"/>
       <c r="E147" s="13" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="F147" s="13" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="G147" s="13" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
@@ -5346,13 +5366,13 @@
         <v>55</v>
       </c>
       <c r="E150" s="17" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F150" s="17" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P150" s="4"/>
       <c r="Q150" s="5"/>
@@ -5363,13 +5383,13 @@
         <v>59</v>
       </c>
       <c r="E151" s="17" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F151" s="17" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P151" s="4"/>
       <c r="Q151" s="5"/>
@@ -5380,13 +5400,13 @@
         <v>60</v>
       </c>
       <c r="E152" s="17" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F152" s="17" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P152" s="4"/>
       <c r="Q152" s="5"/>
@@ -5397,13 +5417,13 @@
         <v>56</v>
       </c>
       <c r="E153" s="17" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F153" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P153" s="4"/>
       <c r="Q153" s="5"/>
@@ -5414,13 +5434,13 @@
         <v>57</v>
       </c>
       <c r="E154" s="17" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="F154" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G154" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P154" s="4"/>
       <c r="Q154" s="5"/>
@@ -5431,13 +5451,13 @@
         <v>58</v>
       </c>
       <c r="E155" s="17" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F155" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G155" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P155" s="4"/>
       <c r="Q155" s="5"/>
@@ -5456,13 +5476,13 @@
         <v>61</v>
       </c>
       <c r="E157" s="17" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F157" s="17" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G157" s="27" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="P157" s="4"/>
       <c r="Q157" s="5"/>
@@ -5473,13 +5493,13 @@
         <v>44</v>
       </c>
       <c r="E158" s="17" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F158" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G158" s="28" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="P158" s="4"/>
       <c r="Q158" s="5"/>
@@ -5487,16 +5507,16 @@
     <row r="159" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C159" s="77"/>
       <c r="D159" s="4" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="E159" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="F159" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="F159" s="17" t="s">
-        <v>209</v>
-      </c>
       <c r="G159" s="36" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="P159" s="4"/>
       <c r="Q159" s="5"/>
@@ -5507,13 +5527,13 @@
         <v>62</v>
       </c>
       <c r="E160" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F160" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G160" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P160" s="4"/>
       <c r="Q160" s="5"/>
@@ -5524,13 +5544,13 @@
         <v>48</v>
       </c>
       <c r="E161" s="17" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="F161" s="17" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G161" s="30" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="P161" s="4"/>
       <c r="Q161" s="5"/>
@@ -5541,13 +5561,13 @@
         <v>63</v>
       </c>
       <c r="E162" s="17" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="F162" s="17" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="G162" s="31" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="P162" s="4"/>
       <c r="Q162" s="5"/>
@@ -5555,16 +5575,16 @@
     <row r="163" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C163" s="89"/>
       <c r="D163" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="E163" s="17" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F163" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G163" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P163" s="4"/>
       <c r="Q163" s="5"/>
@@ -5575,13 +5595,13 @@
         <v>64</v>
       </c>
       <c r="E164" s="17" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="F164" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G164" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P164" s="4"/>
       <c r="Q164" s="5"/>
@@ -5592,13 +5612,13 @@
         <v>10</v>
       </c>
       <c r="E165" s="17" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="F165" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G165" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P165" s="4"/>
       <c r="Q165" s="5"/>
@@ -5609,13 +5629,13 @@
         <v>45</v>
       </c>
       <c r="E166" s="17" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="F166" s="17" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="G166" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P166" s="4"/>
       <c r="Q166" s="5"/>
@@ -5626,13 +5646,13 @@
         <v>43</v>
       </c>
       <c r="E167" s="17" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="F167" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G167" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P167" s="4"/>
       <c r="Q167" s="5"/>
@@ -5643,13 +5663,13 @@
         <v>51</v>
       </c>
       <c r="E168" s="17" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F168" s="17" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G168" s="32" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="P168" s="4"/>
       <c r="Q168" s="5"/>
@@ -5657,16 +5677,16 @@
     <row r="169" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C169" s="89"/>
       <c r="D169" s="1" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E169" s="17" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F169" s="17" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G169" s="42" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="P169" s="4"/>
       <c r="Q169" s="5"/>
@@ -5677,13 +5697,13 @@
         <v>52</v>
       </c>
       <c r="E170" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F170" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G170" s="34" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="P170" s="4"/>
       <c r="Q170" s="5"/>
@@ -5694,13 +5714,13 @@
         <v>65</v>
       </c>
       <c r="E171" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F171" s="17" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G171" s="40" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="P171" s="4"/>
       <c r="Q171" s="5"/>
@@ -5711,13 +5731,13 @@
         <v>53</v>
       </c>
       <c r="E172" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F172" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G172" s="29" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="P172" s="4"/>
       <c r="Q172" s="5"/>
@@ -5728,13 +5748,13 @@
         <v>47</v>
       </c>
       <c r="E173" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F173" s="17" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G173" s="37" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="P173" s="4"/>
       <c r="Q173" s="5"/>
@@ -5753,13 +5773,13 @@
         <v>46</v>
       </c>
       <c r="E175" s="17" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F175" s="17" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G175" s="39" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="P175" s="4"/>
       <c r="Q175" s="5"/>
@@ -5770,13 +5790,13 @@
         <v>1</v>
       </c>
       <c r="E176" s="17" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="F176" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G176" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P176" s="4"/>
       <c r="Q176" s="5"/>
@@ -5787,13 +5807,13 @@
         <v>29</v>
       </c>
       <c r="E177" s="17" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F177" s="17" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="G177" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P177" s="4"/>
       <c r="Q177" s="5"/>
@@ -5804,13 +5824,13 @@
         <v>66</v>
       </c>
       <c r="E178" s="17" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F178" s="17" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="G178" s="38" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="P178" s="4"/>
       <c r="Q178" s="5"/>
@@ -5821,13 +5841,13 @@
         <v>67</v>
       </c>
       <c r="E179" s="17" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F179" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G179" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P179" s="4"/>
       <c r="Q179" s="5"/>
@@ -5838,13 +5858,13 @@
         <v>49</v>
       </c>
       <c r="E180" s="17" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F180" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G180" s="35" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="P180" s="4"/>
       <c r="Q180" s="5"/>
@@ -5855,13 +5875,13 @@
         <v>68</v>
       </c>
       <c r="E181" s="17" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F181" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G181" s="41" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="P181" s="4"/>
       <c r="Q181" s="5"/>
@@ -5872,13 +5892,13 @@
         <v>54</v>
       </c>
       <c r="E182" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F182" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G182" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P182" s="4"/>
       <c r="Q182" s="5"/>
@@ -5889,13 +5909,13 @@
         <v>169</v>
       </c>
       <c r="E183" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F183" s="17" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="G183" s="33" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="P183" s="4"/>
       <c r="Q183" s="5"/>
@@ -5903,16 +5923,16 @@
     <row r="184" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C184" s="89"/>
       <c r="D184" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E184" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F184" s="18" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="G184" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P184" s="4"/>
       <c r="Q184" s="5"/>
@@ -5923,13 +5943,13 @@
         <v>69</v>
       </c>
       <c r="E185" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F185" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G185" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P185" s="4"/>
       <c r="Q185" s="5"/>
@@ -5940,13 +5960,13 @@
         <v>149</v>
       </c>
       <c r="E186" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F186" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G186" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="P186" s="4"/>
       <c r="Q186" s="5"/>
@@ -5962,19 +5982,19 @@
     <row r="188" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C188" s="89"/>
       <c r="D188" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E188" s="17" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F188" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G188" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
@@ -5987,13 +6007,13 @@
         <v>139</v>
       </c>
       <c r="E189" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F189" s="17" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="G189" s="17" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>78</v>
@@ -6006,19 +6026,19 @@
     <row r="190" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C190" s="90"/>
       <c r="D190" s="1" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="E190" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F190" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G190" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
@@ -6028,16 +6048,16 @@
     <row r="191" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C191" s="77"/>
       <c r="D191" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E191" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F191" s="17" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="G191" s="17" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>79</v>
@@ -6050,16 +6070,16 @@
     <row r="192" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C192" s="77"/>
       <c r="D192" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E192" s="17" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="F192" s="17" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="G192" s="17" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="H192" s="3" t="s">
         <v>80</v>
@@ -6073,16 +6093,16 @@
       <c r="B193" s="1"/>
       <c r="C193" s="77"/>
       <c r="D193" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E193" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F193" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G193" s="17" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>184</v>
@@ -6098,13 +6118,13 @@
         <v>101</v>
       </c>
       <c r="E194" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F194" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G194" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>87</v>
@@ -6120,16 +6140,16 @@
         <v>105</v>
       </c>
       <c r="E195" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F195" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G195" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
@@ -6139,19 +6159,19 @@
     <row r="196" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C196" s="90"/>
       <c r="D196" s="1" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="E196" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F196" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G196" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
@@ -6164,13 +6184,13 @@
         <v>104</v>
       </c>
       <c r="E197" s="17" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F197" s="17" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="G197" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H197" s="3" t="s">
         <v>88</v>
@@ -6183,19 +6203,19 @@
     <row r="198" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C198" s="90"/>
       <c r="D198" s="1" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="E198" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F198" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G198" s="43" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
@@ -6205,19 +6225,19 @@
     <row r="199" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C199" s="90"/>
       <c r="D199" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E199" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F199" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G199" s="17" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
@@ -6230,13 +6250,13 @@
         <v>102</v>
       </c>
       <c r="E200" s="52" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F200" s="52" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="G200" s="52" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H200" s="52" t="s">
         <v>77</v>
@@ -6253,16 +6273,16 @@
     <row r="202" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C202" s="77"/>
       <c r="D202" s="19" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E202" s="20" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="F202" s="20" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="G202" s="20" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="H202" s="22"/>
       <c r="I202" s="22"/>
@@ -6273,16 +6293,16 @@
     <row r="203" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C203" s="77"/>
       <c r="D203" s="21" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E203" s="20" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="F203" s="20" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G203" s="20" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="H203" s="22"/>
       <c r="I203" s="22"/>
@@ -6293,16 +6313,16 @@
     <row r="204" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C204" s="89"/>
       <c r="D204" s="23" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E204" s="20" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F204" s="20" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G204" s="20" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="H204" s="22"/>
       <c r="I204" s="22"/>
@@ -6320,15 +6340,15 @@
       <c r="P206" s="4"/>
       <c r="Q206" s="5"/>
     </row>
-    <row r="207" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C207" s="92"/>
       <c r="D207" s="24" t="s">
-        <v>294</v>
-      </c>
-      <c r="E207" s="80" t="s">
-        <v>338</v>
-      </c>
-      <c r="F207" s="80"/>
+        <v>285</v>
+      </c>
+      <c r="E207" s="110" t="s">
+        <v>329</v>
+      </c>
+      <c r="F207" s="110"/>
       <c r="G207" s="80"/>
       <c r="H207" s="80"/>
       <c r="I207" s="80"/>
@@ -6336,15 +6356,15 @@
       <c r="P207" s="4"/>
       <c r="Q207" s="5"/>
     </row>
-    <row r="208" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C208" s="92"/>
       <c r="D208" s="25" t="s">
-        <v>293</v>
-      </c>
-      <c r="E208" s="81" t="s">
-        <v>339</v>
-      </c>
-      <c r="F208" s="81"/>
+        <v>284</v>
+      </c>
+      <c r="E208" s="111" t="s">
+        <v>330</v>
+      </c>
+      <c r="F208" s="111"/>
       <c r="G208" s="81"/>
       <c r="H208" s="81"/>
       <c r="I208" s="81"/>
@@ -6352,15 +6372,15 @@
       <c r="P208" s="4"/>
       <c r="Q208" s="5"/>
     </row>
-    <row r="209" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C209" s="92"/>
       <c r="D209" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="E209" s="81" t="s">
-        <v>295</v>
-      </c>
-      <c r="F209" s="81"/>
+        <v>242</v>
+      </c>
+      <c r="E209" s="111" t="s">
+        <v>286</v>
+      </c>
+      <c r="F209" s="111"/>
       <c r="G209" s="81"/>
       <c r="H209" s="81"/>
       <c r="I209" s="81"/>
@@ -6368,15 +6388,15 @@
       <c r="P209" s="4"/>
       <c r="Q209" s="5"/>
     </row>
-    <row r="210" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C210" s="92"/>
       <c r="D210" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="E210" s="81" t="s">
-        <v>286</v>
-      </c>
-      <c r="F210" s="81"/>
+        <v>283</v>
+      </c>
+      <c r="E210" s="111" t="s">
+        <v>277</v>
+      </c>
+      <c r="F210" s="111"/>
       <c r="G210" s="81"/>
       <c r="H210" s="81"/>
       <c r="I210" s="81"/>
@@ -6384,15 +6404,15 @@
       <c r="P210" s="4"/>
       <c r="Q210" s="5"/>
     </row>
-    <row r="211" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C211" s="77"/>
       <c r="D211" s="26" t="s">
-        <v>291</v>
-      </c>
-      <c r="E211" s="82" t="s">
-        <v>343</v>
-      </c>
-      <c r="F211" s="82"/>
+        <v>282</v>
+      </c>
+      <c r="E211" s="112" t="s">
+        <v>334</v>
+      </c>
+      <c r="F211" s="112"/>
       <c r="G211" s="82"/>
       <c r="H211" s="82"/>
       <c r="I211" s="82"/>
@@ -6400,15 +6420,15 @@
       <c r="P211" s="4"/>
       <c r="Q211" s="5"/>
     </row>
-    <row r="212" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C212" s="77"/>
       <c r="D212" s="26" t="s">
-        <v>275</v>
-      </c>
-      <c r="E212" s="82" t="s">
-        <v>340</v>
-      </c>
-      <c r="F212" s="82"/>
+        <v>266</v>
+      </c>
+      <c r="E212" s="112" t="s">
+        <v>331</v>
+      </c>
+      <c r="F212" s="112"/>
       <c r="G212" s="82"/>
       <c r="H212" s="82"/>
       <c r="I212" s="82"/>
@@ -6416,15 +6436,15 @@
       <c r="P212" s="4"/>
       <c r="Q212" s="5"/>
     </row>
-    <row r="213" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C213" s="77"/>
       <c r="D213" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="E213" s="82" t="s">
-        <v>346</v>
-      </c>
-      <c r="F213" s="82"/>
+        <v>281</v>
+      </c>
+      <c r="E213" s="112" t="s">
+        <v>337</v>
+      </c>
+      <c r="F213" s="112"/>
       <c r="G213" s="82"/>
       <c r="H213" s="82"/>
       <c r="I213" s="82"/>
@@ -6435,12 +6455,12 @@
     <row r="214" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C214" s="89"/>
       <c r="D214" s="26" t="s">
-        <v>289</v>
-      </c>
-      <c r="E214" s="82" t="s">
-        <v>287</v>
-      </c>
-      <c r="F214" s="82"/>
+        <v>280</v>
+      </c>
+      <c r="E214" s="112" t="s">
+        <v>278</v>
+      </c>
+      <c r="F214" s="112"/>
       <c r="G214" s="82"/>
       <c r="H214" s="82"/>
       <c r="I214" s="82"/>
@@ -6453,12 +6473,12 @@
       <c r="B215" s="74"/>
       <c r="C215" s="89"/>
       <c r="D215" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="E215" s="83" t="s">
-        <v>353</v>
-      </c>
-      <c r="F215" s="83"/>
+        <v>325</v>
+      </c>
+      <c r="E215" s="113" t="s">
+        <v>344</v>
+      </c>
+      <c r="F215" s="113"/>
       <c r="G215" s="83"/>
       <c r="H215" s="83"/>
       <c r="I215" s="83"/>
@@ -6471,12 +6491,12 @@
       <c r="B216" s="75"/>
       <c r="C216" s="93"/>
       <c r="D216" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="E216" s="83" t="s">
-        <v>354</v>
-      </c>
-      <c r="F216" s="83"/>
+        <v>237</v>
+      </c>
+      <c r="E216" s="113" t="s">
+        <v>345</v>
+      </c>
+      <c r="F216" s="113"/>
       <c r="G216" s="83"/>
       <c r="H216" s="83"/>
       <c r="I216" s="83"/>
@@ -6489,12 +6509,12 @@
       <c r="B217" s="76"/>
       <c r="C217" s="93"/>
       <c r="D217" s="22" t="s">
-        <v>349</v>
-      </c>
-      <c r="E217" s="83" t="s">
-        <v>350</v>
-      </c>
-      <c r="F217" s="83"/>
+        <v>340</v>
+      </c>
+      <c r="E217" s="113" t="s">
+        <v>341</v>
+      </c>
+      <c r="F217" s="113"/>
       <c r="G217" s="83"/>
       <c r="H217" s="83"/>
       <c r="I217" s="83"/>
@@ -6507,12 +6527,12 @@
       <c r="B218" s="77"/>
       <c r="C218" s="93"/>
       <c r="D218" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="E218" s="83" t="s">
-        <v>355</v>
-      </c>
-      <c r="F218" s="83"/>
+        <v>243</v>
+      </c>
+      <c r="E218" s="113" t="s">
+        <v>346</v>
+      </c>
+      <c r="F218" s="113"/>
       <c r="G218" s="83"/>
       <c r="H218" s="83"/>
       <c r="I218" s="83"/>
@@ -6525,12 +6545,12 @@
       <c r="B219" s="78"/>
       <c r="C219" s="93"/>
       <c r="D219" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="E219" s="83" t="s">
-        <v>323</v>
-      </c>
-      <c r="F219" s="83"/>
+        <v>238</v>
+      </c>
+      <c r="E219" s="113" t="s">
+        <v>314</v>
+      </c>
+      <c r="F219" s="113"/>
       <c r="G219" s="83"/>
       <c r="H219" s="83"/>
       <c r="I219" s="83"/>
@@ -6543,12 +6563,12 @@
       <c r="B220" s="79"/>
       <c r="C220" s="93"/>
       <c r="D220" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="E220" s="83" t="s">
-        <v>324</v>
-      </c>
-      <c r="F220" s="83"/>
+        <v>249</v>
+      </c>
+      <c r="E220" s="113" t="s">
+        <v>315</v>
+      </c>
+      <c r="F220" s="113"/>
       <c r="G220" s="83"/>
       <c r="H220" s="83"/>
       <c r="I220" s="83"/>
@@ -6595,7 +6615,7 @@
     <row r="224" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C224" s="94"/>
       <c r="D224" s="3" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="E224" s="12"/>
       <c r="F224" s="12"/>
@@ -6610,10 +6630,10 @@
     <row r="225" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C225" s="95"/>
       <c r="D225" s="3" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="E225" s="12" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="F225" s="12"/>
       <c r="G225" s="12"/>
@@ -6627,10 +6647,10 @@
     <row r="226" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C226" s="96"/>
       <c r="D226" s="3" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E226" s="84" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F226" s="12"/>
       <c r="G226" s="12"/>
@@ -6644,10 +6664,10 @@
     <row r="227" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C227" s="97"/>
       <c r="D227" s="3" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="E227" s="84" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="F227" s="12"/>
       <c r="G227" s="12"/>
@@ -6661,10 +6681,10 @@
     <row r="228" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C228" s="98"/>
       <c r="D228" s="3" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E228" s="84" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F228" s="12"/>
       <c r="G228" s="12"/>
@@ -6677,10 +6697,10 @@
     <row r="229" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C229" s="99"/>
       <c r="D229" s="3" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E229" s="84" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="F229" s="12"/>
       <c r="G229" s="12"/>
@@ -6777,16 +6797,16 @@
       <c r="C237" s="11"/>
       <c r="D237" s="100"/>
       <c r="E237" s="1" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="H237" s="4" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="I237" s="12"/>
       <c r="J237" s="12"/>
@@ -6800,16 +6820,16 @@
         <v>178</v>
       </c>
       <c r="E238" s="54" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="F238" s="54" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="G238" s="54" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="H238" s="54" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="I238" s="12"/>
       <c r="J238" s="12"/>
@@ -6823,16 +6843,16 @@
         <v>177</v>
       </c>
       <c r="E239" s="55" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="F239" s="66" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="G239" s="66" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="H239" s="66" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="I239" s="12"/>
       <c r="J239" s="12"/>
@@ -6843,19 +6863,19 @@
     <row r="240" spans="3:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C240" s="11"/>
       <c r="D240" s="5" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="E240" s="56" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="F240" s="56" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="G240" s="56" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="H240" s="56" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="J240" s="12"/>
       <c r="K240" s="2"/>
@@ -6865,19 +6885,19 @@
     <row r="241" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C241" s="11"/>
       <c r="D241" s="5" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E241" s="63" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="F241" s="101" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="G241" s="101" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="H241" s="69" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="J241" s="12"/>
       <c r="K241" s="2"/>
@@ -6890,16 +6910,16 @@
         <v>105</v>
       </c>
       <c r="E242" s="62" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F242" s="62" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="G242" s="62" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="H242" s="62" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="J242" s="12"/>
       <c r="K242" s="2"/>
@@ -6909,19 +6929,19 @@
     <row r="243" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C243" s="11"/>
       <c r="D243" s="5" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="E243" s="58" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="F243" s="58" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="G243" s="58" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="H243" s="58" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="J243" s="12"/>
       <c r="K243" s="2"/>
@@ -6934,16 +6954,16 @@
         <v>176</v>
       </c>
       <c r="E244" s="65" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="F244" s="65" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="G244" s="65" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H244" s="65" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="J244" s="12"/>
       <c r="K244" s="2"/>
@@ -6956,16 +6976,16 @@
         <v>175</v>
       </c>
       <c r="E245" s="64" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="F245" s="64" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="G245" s="64" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="H245" s="67" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="J245" s="12"/>
       <c r="K245" s="2"/>
@@ -6978,16 +6998,16 @@
         <v>171</v>
       </c>
       <c r="E246" s="57" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="F246" s="70" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="G246" s="70" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="H246" s="57" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="I246" s="12"/>
       <c r="J246" s="12"/>
@@ -6998,19 +7018,19 @@
     <row r="247" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C247" s="11"/>
       <c r="D247" s="5" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="E247" s="59" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="F247" s="59" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="G247" s="59" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="H247" s="59" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="I247" s="12"/>
       <c r="J247" s="12"/>
@@ -7024,16 +7044,16 @@
         <v>172</v>
       </c>
       <c r="E248" s="60" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F248" s="60" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="G248" s="60" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="H248" s="60" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="I248" s="12"/>
       <c r="J248" s="12"/>
@@ -7047,16 +7067,16 @@
         <v>173</v>
       </c>
       <c r="E249" s="61" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="F249" s="61" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G249" s="61" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="H249" s="61" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="I249" s="12"/>
       <c r="J249" s="12"/>
@@ -7066,19 +7086,19 @@
     </row>
     <row r="250" spans="2:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D250" s="5" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E250" s="71" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="F250" s="71" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="G250" s="71" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="H250" s="71" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="J250" s="85"/>
       <c r="K250" s="100"/>
@@ -7124,16 +7144,16 @@
         <v>178</v>
       </c>
       <c r="E254" s="54" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="F254" s="54" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="G254" s="54" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="H254" s="54" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="I254" s="11"/>
       <c r="L254" s="100"/>
@@ -7148,16 +7168,16 @@
         <v>176</v>
       </c>
       <c r="E255" s="44" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="F255" s="44" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="G255" s="44" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="H255" s="44" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="L255" s="100"/>
       <c r="M255" s="100"/>
@@ -7171,19 +7191,19 @@
         <v>175</v>
       </c>
       <c r="E256" s="44" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="F256" s="44" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="G256" s="44" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="H256" s="44" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="J256" s="44" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="L256" s="100"/>
       <c r="M256" s="100"/>
@@ -7192,19 +7212,19 @@
     </row>
     <row r="257" spans="2:18" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" s="3" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="F257" s="44" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="G257" s="44" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="H257" s="44" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="J257" s="44" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="L257" s="100"/>
       <c r="M257" s="100"/>
@@ -7216,13 +7236,13 @@
         <v>173</v>
       </c>
       <c r="E258" s="44" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="G258" s="44" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="J258" s="44" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="L258" s="100"/>
       <c r="M258" s="100"/>
@@ -7235,10 +7255,10 @@
       </c>
       <c r="D259" s="5"/>
       <c r="E259" s="44" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="G259" s="44" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="I259" s="72"/>
       <c r="L259" s="100"/>
@@ -7248,14 +7268,14 @@
     </row>
     <row r="260" spans="2:18" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B260" s="3" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="D260" s="5"/>
       <c r="E260" s="44" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="G260" s="44" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="I260" s="72"/>
       <c r="L260" s="100"/>
@@ -7282,16 +7302,16 @@
         <v>177</v>
       </c>
       <c r="E262" s="55" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="F262" s="66" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="G262" s="66" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="H262" s="66" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="I262" s="11"/>
       <c r="L262" s="100"/>
@@ -7305,16 +7325,16 @@
       </c>
       <c r="D263" s="5"/>
       <c r="E263" s="44" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="F263" s="44" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="G263" s="44" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="H263" s="44" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="I263" s="72"/>
       <c r="L263" s="100"/>
@@ -7324,24 +7344,24 @@
     </row>
     <row r="264" spans="2:18" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B264" s="3" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="D264" s="5"/>
       <c r="E264" s="44" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="F264" s="44" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="G264" s="44" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="H264" s="44" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="I264" s="72"/>
       <c r="J264" s="44" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="L264" s="100"/>
       <c r="M264" s="100"/>
@@ -7352,17 +7372,17 @@
       <c r="B265" s="3"/>
       <c r="D265" s="5"/>
       <c r="F265" s="44" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="G265" s="44" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="H265" s="44" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="I265" s="72"/>
       <c r="J265" s="44" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="L265" s="100"/>
       <c r="M265" s="100"/>
@@ -7373,7 +7393,7 @@
       <c r="B266" s="3"/>
       <c r="D266" s="5"/>
       <c r="E266" s="44" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="I266" s="72"/>
       <c r="L266" s="100"/>
@@ -7387,7 +7407,7 @@
       </c>
       <c r="D267" s="5"/>
       <c r="E267" s="44" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="I267" s="72"/>
       <c r="L267" s="100"/>
@@ -7401,7 +7421,7 @@
       </c>
       <c r="D268" s="5"/>
       <c r="E268" s="44" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="I268" s="72"/>
       <c r="L268" s="100"/>
@@ -7428,16 +7448,16 @@
         <v>175</v>
       </c>
       <c r="E270" s="64" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="F270" s="64" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="G270" s="64" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="H270" s="67" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="I270" s="11"/>
       <c r="L270" s="100"/>
@@ -7448,20 +7468,20 @@
     </row>
     <row r="271" spans="2:18" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B271" s="5" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="D271" s="5"/>
       <c r="E271" s="44" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="F271" s="44" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="G271" s="73" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="H271" s="44" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="I271" s="72"/>
       <c r="L271" s="100"/>
@@ -7475,20 +7495,20 @@
       </c>
       <c r="D272" s="5"/>
       <c r="E272" s="44" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="F272" s="44" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="G272" s="44" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="H272" s="44" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="I272" s="72"/>
       <c r="J272" s="44" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="L272" s="100"/>
       <c r="M272" s="100"/>
@@ -7501,14 +7521,14 @@
       </c>
       <c r="D273" s="5"/>
       <c r="G273" s="44" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="H273" s="44" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="I273" s="72"/>
       <c r="J273" s="44" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="L273" s="100"/>
       <c r="M273" s="100"/>
@@ -7521,10 +7541,10 @@
       </c>
       <c r="D274" s="5"/>
       <c r="E274" s="44" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="G274" s="44" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="I274" s="72"/>
       <c r="L274" s="100"/>
@@ -7534,14 +7554,14 @@
     </row>
     <row r="275" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B275" s="5" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D275" s="5"/>
       <c r="E275" s="44" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
       <c r="G275" s="44" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="I275" s="72"/>
       <c r="L275" s="100"/>
@@ -7551,14 +7571,14 @@
     </row>
     <row r="276" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B276" s="5" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="D276" s="5"/>
       <c r="E276" s="44" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="G276" s="44" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="I276" s="72"/>
       <c r="L276" s="100"/>
@@ -7579,22 +7599,22 @@
     </row>
     <row r="278" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B278" s="5" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="D278" s="5" t="s">
         <v>176</v>
       </c>
       <c r="E278" s="65" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="F278" s="65" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="G278" s="65" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H278" s="65" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="I278" s="11"/>
       <c r="L278" s="100"/>
@@ -7608,13 +7628,13 @@
       </c>
       <c r="D279" s="5"/>
       <c r="E279" s="44" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="G279" s="44" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="H279" s="44" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="I279" s="72"/>
       <c r="J279" s="3"/>
@@ -7626,10 +7646,10 @@
     <row r="280" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D280" s="5"/>
       <c r="G280" s="44" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="H280" s="44" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="I280" s="72"/>
       <c r="J280" s="3"/>
@@ -7641,10 +7661,10 @@
     <row r="281" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D281" s="5"/>
       <c r="G281" s="44" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="H281" s="44" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="I281" s="72"/>
       <c r="J281" s="3"/>
@@ -7656,7 +7676,7 @@
     <row r="282" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D282" s="5"/>
       <c r="G282" s="44" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="I282" s="72"/>
       <c r="J282" s="3"/>
@@ -7668,10 +7688,10 @@
     <row r="283" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D283" s="5"/>
       <c r="E283" s="44" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="G283" s="44" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="I283" s="72"/>
       <c r="L283" s="100"/>
@@ -7682,10 +7702,10 @@
     <row r="284" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D284" s="5"/>
       <c r="E284" s="44" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="G284" s="44" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="I284" s="72"/>
       <c r="L284" s="100"/>
@@ -7703,19 +7723,19 @@
     </row>
     <row r="286" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D286" s="5" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="E286" s="66" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="F286" s="66" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="G286" s="68" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="H286" s="69" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="I286" s="11"/>
       <c r="L286" s="100"/>
@@ -7726,13 +7746,13 @@
     <row r="287" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D287" s="5"/>
       <c r="F287" s="44" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="G287" s="44" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="H287" s="44" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
       <c r="I287" s="72"/>
       <c r="L287" s="100"/>
@@ -7743,13 +7763,13 @@
     <row r="288" spans="2:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D288" s="5"/>
       <c r="F288" s="44" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="G288" s="44" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="H288" s="44" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="I288" s="72"/>
       <c r="L288" s="100"/>
@@ -7760,16 +7780,16 @@
     <row r="289" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D289" s="5"/>
       <c r="E289" s="44" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="F289" s="44" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="G289" s="44" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="H289" s="44" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="I289" s="72"/>
       <c r="L289" s="100"/>
@@ -7780,10 +7800,10 @@
     <row r="290" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D290" s="5"/>
       <c r="E290" s="44" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="G290" s="44" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="I290" s="72"/>
       <c r="L290" s="100"/>
@@ -7794,10 +7814,10 @@
     <row r="291" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D291" s="5"/>
       <c r="E291" s="44" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="G291" s="44" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="I291" s="72"/>
       <c r="L291" s="100"/>
@@ -7808,10 +7828,10 @@
     <row r="292" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D292" s="5"/>
       <c r="E292" s="44" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="G292" s="44" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="I292" s="72"/>
       <c r="L292" s="100"/>
@@ -7832,16 +7852,16 @@
         <v>105</v>
       </c>
       <c r="E294" s="62" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="F294" s="62" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="G294" s="62" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="H294" s="62" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="I294" s="11"/>
       <c r="L294" s="100"/>
@@ -7852,10 +7872,10 @@
     <row r="295" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D295" s="5"/>
       <c r="E295" s="44" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="F295" s="44" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="I295" s="72"/>
       <c r="L295" s="100"/>
@@ -7866,10 +7886,10 @@
     <row r="296" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D296" s="5"/>
       <c r="E296" s="44" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="F296" s="44" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="I296" s="72"/>
       <c r="L296" s="100"/>
@@ -7880,10 +7900,10 @@
     <row r="297" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D297" s="5"/>
       <c r="E297" s="44" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="F297" s="44" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="I297" s="72"/>
       <c r="L297" s="100"/>
@@ -7894,7 +7914,7 @@
     <row r="298" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D298" s="5"/>
       <c r="E298" s="44" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="I298" s="72"/>
       <c r="L298" s="100"/>
@@ -7905,7 +7925,7 @@
     <row r="299" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D299" s="5"/>
       <c r="E299" s="44" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="I299" s="72"/>
       <c r="L299" s="100"/>
@@ -7916,7 +7936,7 @@
     <row r="300" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D300" s="5"/>
       <c r="E300" s="44" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="I300" s="72"/>
       <c r="L300" s="100"/>
@@ -7936,17 +7956,17 @@
       <c r="D302" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E302" s="105" t="s">
-        <v>370</v>
-      </c>
-      <c r="F302" s="106" t="s">
-        <v>602</v>
+      <c r="E302" s="104" t="s">
+        <v>361</v>
+      </c>
+      <c r="F302" s="105" t="s">
+        <v>586</v>
       </c>
       <c r="G302" s="70" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="H302" s="57" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="I302" s="72"/>
       <c r="L302" s="100"/>
@@ -7957,16 +7977,16 @@
     <row r="303" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D303" s="5"/>
       <c r="E303" s="44" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="F303" s="44" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="G303" s="44" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="H303" s="44" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="I303" s="72"/>
       <c r="L303" s="100"/>
@@ -7977,13 +7997,13 @@
     <row r="304" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D304" s="5"/>
       <c r="F304" s="44" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="G304" s="44" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="H304" s="44" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
       <c r="I304" s="72"/>
       <c r="L304" s="100"/>
@@ -7994,10 +8014,10 @@
     <row r="305" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D305" s="5"/>
       <c r="G305" s="44" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="H305" s="44" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="I305" s="72"/>
       <c r="L305" s="100"/>
@@ -8008,7 +8028,7 @@
     <row r="306" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D306" s="5"/>
       <c r="G306" s="44" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="I306" s="72"/>
       <c r="L306" s="100"/>
@@ -8019,10 +8039,10 @@
     <row r="307" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D307" s="5"/>
       <c r="E307" s="44" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="G307" s="44" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="I307" s="72"/>
       <c r="L307" s="100"/>
@@ -8033,10 +8053,10 @@
     <row r="308" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D308" s="5"/>
       <c r="E308" s="44" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="G308" s="44" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="I308" s="72"/>
       <c r="L308" s="100"/>
@@ -8057,19 +8077,19 @@
         <v>172</v>
       </c>
       <c r="E310" s="60" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F310" s="60" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="G310" s="60" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="H310" s="60" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="I310" s="72" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="L310" s="100"/>
       <c r="M310" s="100"/>
@@ -8079,13 +8099,13 @@
     <row r="311" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D311" s="5"/>
       <c r="E311" s="44" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="F311" s="44" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="G311" s="44" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="I311" s="72"/>
       <c r="L311" s="100"/>
@@ -8096,13 +8116,13 @@
     <row r="312" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D312" s="5"/>
       <c r="E312" s="44" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="F312" s="44" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="G312" s="44" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="I312" s="72"/>
       <c r="L312" s="100"/>
@@ -8113,10 +8133,10 @@
     <row r="313" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D313" s="5"/>
       <c r="F313" s="44" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="G313" s="44" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="I313" s="72"/>
       <c r="L313" s="100"/>
@@ -8127,7 +8147,7 @@
     <row r="314" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D314" s="5"/>
       <c r="G314" s="44" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="I314" s="72"/>
       <c r="L314" s="100"/>
@@ -8138,7 +8158,7 @@
     <row r="315" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D315" s="5"/>
       <c r="G315" s="44" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="I315" s="72"/>
       <c r="L315" s="100"/>
@@ -8149,7 +8169,7 @@
     <row r="316" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D316" s="5"/>
       <c r="G316" s="44" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
       <c r="I316" s="72"/>
       <c r="L316" s="100"/>
@@ -8161,17 +8181,17 @@
       <c r="D317" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="E317" s="108" t="s">
-        <v>359</v>
-      </c>
-      <c r="F317" s="107" t="s">
-        <v>609</v>
+      <c r="E317" s="107" t="s">
+        <v>350</v>
+      </c>
+      <c r="F317" s="106" t="s">
+        <v>593</v>
       </c>
       <c r="G317" s="61" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="H317" s="61" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="I317" s="72" t="s">
         <v>50</v>
@@ -8184,13 +8204,13 @@
     <row r="318" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D318" s="5"/>
       <c r="E318" s="44" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="F318" s="44" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
       <c r="G318" s="44" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
       <c r="I318" s="72"/>
       <c r="L318" s="100"/>
@@ -8201,13 +8221,13 @@
     <row r="319" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D319" s="5"/>
       <c r="E319" s="44" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="F319" s="44" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="G319" s="44" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="I319" s="72"/>
       <c r="L319" s="100"/>
@@ -8218,10 +8238,10 @@
     <row r="320" spans="4:15" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D320" s="5"/>
       <c r="E320" s="44" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="G320" s="44" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="I320" s="72"/>
       <c r="L320" s="100"/>
@@ -8232,7 +8252,7 @@
     <row r="321" spans="4:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D321" s="5"/>
       <c r="G321" s="44" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="I321" s="72"/>
       <c r="L321" s="100"/>
@@ -8243,7 +8263,7 @@
     <row r="322" spans="4:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D322" s="5"/>
       <c r="G322" s="44" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="I322" s="72"/>
       <c r="L322" s="100"/>
@@ -8269,19 +8289,19 @@
     </row>
     <row r="325" spans="4:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D325" s="5" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E325" s="71" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="F325" s="71" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="G325" s="71" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="H325" s="71" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="I325" s="72" t="s">
         <v>50</v>
@@ -8302,7 +8322,7 @@
     <row r="327" spans="4:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D327" s="5"/>
       <c r="E327" s="44" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="I327" s="72"/>
       <c r="L327" s="100"/>
@@ -8387,16 +8407,16 @@
     <row r="336" spans="4:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D336" s="5"/>
       <c r="E336" s="54" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="F336" s="54" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="G336" s="54" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="H336" s="54" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="I336" s="72"/>
       <c r="L336" s="100"/>
@@ -8409,16 +8429,16 @@
     <row r="337" spans="3:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D337" s="5"/>
       <c r="E337" s="55" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="F337" s="66" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="G337" s="66" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="H337" s="66" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="I337" s="72"/>
       <c r="L337" s="100"/>
@@ -8431,16 +8451,16 @@
     <row r="338" spans="3:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D338" s="5"/>
       <c r="E338" s="64" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="F338" s="64" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="G338" s="64" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="H338" s="67" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="I338" s="72"/>
       <c r="L338" s="100"/>
@@ -8453,16 +8473,16 @@
     <row r="339" spans="3:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D339" s="5"/>
       <c r="E339" s="65" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="F339" s="65" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="G339" s="65" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="H339" s="65" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="I339" s="72"/>
       <c r="L339" s="100"/>
@@ -8475,16 +8495,16 @@
     <row r="340" spans="3:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D340" s="5"/>
       <c r="E340" s="66" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="F340" s="66" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="G340" s="68" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="H340" s="69" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="I340" s="72"/>
       <c r="L340" s="100"/>
@@ -8497,16 +8517,16 @@
     <row r="341" spans="3:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D341" s="5"/>
       <c r="E341" s="62" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="F341" s="62" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="G341" s="62" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="H341" s="62" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="I341" s="72"/>
       <c r="L341" s="100"/>
@@ -8519,16 +8539,16 @@
     <row r="342" spans="3:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D342" s="5"/>
       <c r="E342" s="57" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="F342" s="70" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="G342" s="70" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="H342" s="57" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="I342" s="72"/>
       <c r="L342" s="100"/>
@@ -8541,16 +8561,16 @@
     <row r="343" spans="3:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D343" s="5"/>
       <c r="E343" s="60" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="F343" s="60" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="G343" s="60" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="H343" s="60" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="I343" s="72"/>
       <c r="L343" s="100"/>
@@ -8562,16 +8582,16 @@
     </row>
     <row r="344" spans="3:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E344" s="61" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="F344" s="61" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G344" s="61" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="H344" s="61" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="J344" s="85"/>
       <c r="K344" s="100"/>
@@ -8584,16 +8604,16 @@
     </row>
     <row r="345" spans="3:17" s="44" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E345" s="71" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="F345" s="71" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="G345" s="71" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="H345" s="71" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="J345" s="85"/>
       <c r="K345" s="100"/>
@@ -8799,7 +8819,7 @@
       </c>
       <c r="H361" s="3"/>
       <c r="I361" s="4" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="J361" s="1" t="s">
         <v>45</v>
@@ -8822,7 +8842,7 @@
       </c>
       <c r="H362" s="3"/>
       <c r="I362" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="P362" s="4"/>
       <c r="Q362" s="5"/>
@@ -8961,7 +8981,7 @@
         <v>10</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="K370" s="4" t="s">
         <v>61</v>
@@ -9100,10 +9120,10 @@
         <v>10</v>
       </c>
       <c r="J376" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="L376" s="3"/>
       <c r="M376" s="3"/>
@@ -9149,7 +9169,7 @@
       </c>
       <c r="H378" s="3"/>
       <c r="I378" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="J378" s="1" t="s">
         <v>63</v>
@@ -9185,7 +9205,7 @@
         <v>115</v>
       </c>
       <c r="F380" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G380" s="6" t="s">
         <v>101</v>
@@ -9286,7 +9306,7 @@
         <v>104</v>
       </c>
       <c r="G385" s="6" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="H385" s="3" t="s">
         <v>148</v>
@@ -11291,8 +11311,134 @@
       <c r="Q537" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="127">
+    <mergeCell ref="E219:F219"/>
+    <mergeCell ref="E220:F220"/>
+    <mergeCell ref="E207:F207"/>
+    <mergeCell ref="E208:F208"/>
+    <mergeCell ref="E209:F209"/>
+    <mergeCell ref="E210:F210"/>
+    <mergeCell ref="E211:F211"/>
+    <mergeCell ref="E212:F212"/>
+    <mergeCell ref="E213:F213"/>
+    <mergeCell ref="E214:F214"/>
+    <mergeCell ref="E215:F215"/>
+    <mergeCell ref="E216:F216"/>
+    <mergeCell ref="E217:F217"/>
+    <mergeCell ref="E218:F218"/>
+    <mergeCell ref="H121:J121"/>
+    <mergeCell ref="H122:J122"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="H109:J109"/>
+    <mergeCell ref="H111:J111"/>
+    <mergeCell ref="H110:J110"/>
+    <mergeCell ref="H112:J112"/>
+    <mergeCell ref="H113:J113"/>
+    <mergeCell ref="H114:J114"/>
+    <mergeCell ref="H115:J115"/>
+    <mergeCell ref="H116:J116"/>
+    <mergeCell ref="H117:J117"/>
+    <mergeCell ref="H118:J118"/>
+    <mergeCell ref="H119:J119"/>
+    <mergeCell ref="H120:J120"/>
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="H83:J83"/>
+    <mergeCell ref="H84:J84"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="H69:J69"/>
+    <mergeCell ref="H70:J70"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="H95:J95"/>
+    <mergeCell ref="H94:J94"/>
+    <mergeCell ref="H93:J93"/>
+    <mergeCell ref="H92:J92"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="H91:J91"/>
+    <mergeCell ref="H85:J85"/>
+    <mergeCell ref="H86:J86"/>
+    <mergeCell ref="H87:J87"/>
+    <mergeCell ref="H88:J88"/>
+    <mergeCell ref="H89:J89"/>
+    <mergeCell ref="H90:J90"/>
+    <mergeCell ref="H101:J101"/>
+    <mergeCell ref="H100:J100"/>
+    <mergeCell ref="H99:J99"/>
+    <mergeCell ref="H98:J98"/>
+    <mergeCell ref="H96:J96"/>
+    <mergeCell ref="H97:J97"/>
+    <mergeCell ref="H108:J108"/>
+    <mergeCell ref="H106:J106"/>
+    <mergeCell ref="H105:J105"/>
+    <mergeCell ref="H104:J104"/>
+    <mergeCell ref="H102:J102"/>
+    <mergeCell ref="H107:J107"/>
+    <mergeCell ref="H103:J103"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="F95:G95"/>
     <mergeCell ref="N65:P65"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F71:G71"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
